--- a/filter-cases/final_img/5x5/metrics_5x5.xlsx
+++ b/filter-cases/final_img/5x5/metrics_5x5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\fysiko_apth\ptuxiaki\thesis-cases\final_img\5x5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698D7B2C-4F53-4547-8364-756DC176936C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35352BA4-3298-4E5E-8848-398ADC170D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30132" yWindow="588" windowWidth="23040" windowHeight="11976" xr2:uid="{1A5AD2DC-DE0B-4FFA-AE19-FC07F326EFA1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
   <si>
     <t>output text</t>
   </si>
@@ -821,21 +821,57 @@
       <c r="C9" t="s">
         <v>37</v>
       </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9">
+        <v>32508</v>
+      </c>
+      <c r="J9">
+        <v>14574</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>68</v>
+      </c>
+      <c r="M9">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="N9">
+        <v>1485</v>
+      </c>
+      <c r="O9">
+        <v>179224</v>
+      </c>
       <c r="P9">
         <f>N9+($F$2*$E$2)</f>
-        <v>175812</v>
+        <v>177297</v>
       </c>
       <c r="Q9">
-        <f>1000/(T9-M9)</f>
-        <v>76.92307692307692</v>
+        <f>1000/(T9-O9)</f>
+        <v>-5.5800146196383037E-3</v>
       </c>
       <c r="R9">
         <f>U9*Q9</f>
-        <v>76.92307692307692</v>
+        <v>-5.5800146196383037E-3</v>
       </c>
       <c r="S9">
         <f>Q9*10^6/P9</f>
-        <v>437.53029897320386</v>
+        <v>-3.1472696208273712E-2</v>
       </c>
       <c r="T9">
         <v>13</v>
@@ -854,21 +890,57 @@
       <c r="C11" t="s">
         <v>40</v>
       </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>0.49991467595100397</v>
+      </c>
+      <c r="F11">
+        <v>0.70704644918441695</v>
+      </c>
+      <c r="G11">
+        <v>0.99883667465734205</v>
+      </c>
+      <c r="H11">
+        <v>51.141844773077203</v>
+      </c>
+      <c r="I11">
+        <v>4540</v>
+      </c>
+      <c r="J11">
+        <v>12173</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>2.8690000000000002</v>
+      </c>
+      <c r="N11">
+        <v>1479</v>
+      </c>
+      <c r="O11">
+        <v>179218</v>
+      </c>
       <c r="P11">
         <f>N11+($F$2*$E$2)</f>
-        <v>175812</v>
+        <v>177291</v>
       </c>
       <c r="Q11">
         <f>1000/(T11-M11)</f>
-        <v>76.92307692307692</v>
+        <v>98.706939097818577</v>
       </c>
       <c r="R11">
         <f t="shared" ref="R11" si="0">U11*Q11</f>
-        <v>76.92307692307692</v>
+        <v>98.706939097818577</v>
       </c>
       <c r="S11">
         <f>Q11*10^6/P11</f>
-        <v>437.53029897320386</v>
+        <v>556.7509862193715</v>
       </c>
       <c r="T11">
         <v>13</v>

--- a/filter-cases/final_img/5x5/metrics_5x5.xlsx
+++ b/filter-cases/final_img/5x5/metrics_5x5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\fysiko_apth\ptuxiaki\thesis-cases\final_img\5x5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35352BA4-3298-4E5E-8848-398ADC170D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A559F514-0057-4985-8CD1-971EB95ADEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30132" yWindow="588" windowWidth="23040" windowHeight="11976" xr2:uid="{1A5AD2DC-DE0B-4FFA-AE19-FC07F326EFA1}"/>
+    <workbookView xWindow="-23280" yWindow="2784" windowWidth="23004" windowHeight="11976" xr2:uid="{1A5AD2DC-DE0B-4FFA-AE19-FC07F326EFA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -959,21 +959,57 @@
       <c r="C12" t="s">
         <v>43</v>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0.49991467595100397</v>
+      </c>
+      <c r="F12">
+        <v>0.70704644918441695</v>
+      </c>
+      <c r="G12">
+        <v>0.99883667465734205</v>
+      </c>
+      <c r="H12">
+        <v>51.141844773077203</v>
+      </c>
+      <c r="I12">
+        <v>21293</v>
+      </c>
+      <c r="J12">
+        <v>13643</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>44</v>
+      </c>
+      <c r="M12">
+        <v>1.7609999999999999</v>
+      </c>
+      <c r="N12">
+        <v>1485</v>
+      </c>
+      <c r="O12">
+        <v>179224</v>
+      </c>
       <c r="P12">
         <f>N12+($F$2*$E$2)</f>
-        <v>175812</v>
+        <v>177297</v>
       </c>
       <c r="Q12">
         <f>1000/(T12-M12)</f>
-        <v>76.92307692307692</v>
+        <v>88.975887534478147</v>
       </c>
       <c r="R12">
         <f>U12*Q12</f>
-        <v>76.92307692307692</v>
+        <v>88.975887534478147</v>
       </c>
       <c r="S12">
         <f>Q12*10^6/P12</f>
-        <v>437.53029897320386</v>
+        <v>501.84654864142169</v>
       </c>
       <c r="T12">
         <v>13</v>

--- a/filter-cases/final_img/5x5/metrics_5x5.xlsx
+++ b/filter-cases/final_img/5x5/metrics_5x5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\fysiko_apth\ptuxiaki\thesis-cases\final_img\5x5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A559F514-0057-4985-8CD1-971EB95ADEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E5ED0E-AD83-40AB-809A-517867EB32B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23280" yWindow="2784" windowWidth="23004" windowHeight="11976" xr2:uid="{1A5AD2DC-DE0B-4FFA-AE19-FC07F326EFA1}"/>
+    <workbookView xWindow="-30108" yWindow="2892" windowWidth="16728" windowHeight="9828" xr2:uid="{1A5AD2DC-DE0B-4FFA-AE19-FC07F326EFA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>output text</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>smeagol_verilog_rec_cascade_5x5_ieee</t>
+  </si>
+  <si>
+    <t>372x491</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -266,6 +269,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -600,12 +605,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7225027-CB40-48EE-B4E7-9AA397931008}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.86328125" customWidth="1"/>
     <col min="2" max="2" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.3984375" customWidth="1"/>
     <col min="7" max="7" width="10.53125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.53125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="19.1328125" bestFit="1" customWidth="1"/>
@@ -653,6 +658,11 @@
         <v>483</v>
       </c>
     </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="C3" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.45">
       <c r="D6" s="2" t="s">
         <v>2</v>
@@ -768,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="I8">
-        <v>4685</v>
+        <v>4674</v>
       </c>
       <c r="J8">
         <v>12173</v>
@@ -780,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>1.6479999999999999</v>
+        <v>2.1920000000000002</v>
       </c>
       <c r="N8">
         <v>1479</v>
@@ -794,18 +804,18 @@
       </c>
       <c r="Q8">
         <f>1000/(T8-M8)</f>
-        <v>88.090204369274133</v>
+        <v>56.154537286612758</v>
       </c>
       <c r="R8">
         <f>U8*Q8</f>
-        <v>88.090204369274133</v>
+        <v>56.154537286612758</v>
       </c>
       <c r="S8">
         <f>Q8*10^6/P8</f>
-        <v>496.86788595740416</v>
+        <v>316.73653646610802</v>
       </c>
       <c r="T8">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U8">
         <v>1</v>
@@ -837,19 +847,19 @@
         <v>27</v>
       </c>
       <c r="I9">
-        <v>32508</v>
+        <v>32232</v>
       </c>
       <c r="J9">
-        <v>14574</v>
+        <v>14556</v>
       </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M9">
-        <v>0.19400000000000001</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="N9">
         <v>1485</v>
@@ -862,19 +872,19 @@
         <v>177297</v>
       </c>
       <c r="Q9">
-        <f>1000/(T9-O9)</f>
-        <v>-5.5800146196383037E-3</v>
+        <f>1000/(T9-M9)</f>
+        <v>52.562417871222081</v>
       </c>
       <c r="R9">
         <f>U9*Q9</f>
-        <v>-5.5800146196383037E-3</v>
+        <v>52.562417871222081</v>
       </c>
       <c r="S9">
         <f>Q9*10^6/P9</f>
-        <v>-3.1472696208273712E-2</v>
+        <v>296.46535401739499</v>
       </c>
       <c r="T9">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U9">
         <v>1</v>
@@ -918,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2.8690000000000002</v>
+        <v>5.16</v>
       </c>
       <c r="N11">
         <v>1479</v>
@@ -932,18 +942,18 @@
       </c>
       <c r="Q11">
         <f>1000/(T11-M11)</f>
-        <v>98.706939097818577</v>
+        <v>67.385444743935309</v>
       </c>
       <c r="R11">
         <f t="shared" ref="R11" si="0">U11*Q11</f>
-        <v>98.706939097818577</v>
+        <v>67.385444743935309</v>
       </c>
       <c r="S11">
         <f>Q11*10^6/P11</f>
-        <v>556.7509862193715</v>
+        <v>380.08384375932968</v>
       </c>
       <c r="T11">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U11">
         <v>1</v>
@@ -975,7 +985,7 @@
         <v>51.141844773077203</v>
       </c>
       <c r="I12">
-        <v>21293</v>
+        <v>21284</v>
       </c>
       <c r="J12">
         <v>13643</v>
@@ -987,7 +997,7 @@
         <v>44</v>
       </c>
       <c r="M12">
-        <v>1.7609999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="N12">
         <v>1485</v>
@@ -1001,18 +1011,18 @@
       </c>
       <c r="Q12">
         <f>1000/(T12-M12)</f>
-        <v>88.975887534478147</v>
+        <v>59.417706476530014</v>
       </c>
       <c r="R12">
         <f>U12*Q12</f>
-        <v>88.975887534478147</v>
+        <v>59.417706476530014</v>
       </c>
       <c r="S12">
         <f>Q12*10^6/P12</f>
-        <v>501.84654864142169</v>
+        <v>335.13091860849318</v>
       </c>
       <c r="T12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U12">
         <v>1</v>
@@ -1028,24 +1038,60 @@
       <c r="C14" t="s">
         <v>46</v>
       </c>
+      <c r="D14">
+        <v>255</v>
+      </c>
+      <c r="E14">
+        <v>2481.29638671875</v>
+      </c>
+      <c r="F14">
+        <v>49.812614440917898</v>
+      </c>
+      <c r="G14">
+        <v>0.29470688797607902</v>
+      </c>
+      <c r="H14">
+        <v>14.1840186355345</v>
+      </c>
+      <c r="I14">
+        <v>9287</v>
+      </c>
+      <c r="J14">
+        <v>24531</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>1.7290000000000001</v>
+      </c>
+      <c r="N14">
+        <v>2997</v>
+      </c>
+      <c r="O14">
+        <v>182656</v>
+      </c>
       <c r="P14">
         <f t="shared" ref="P14:P15" si="1">N14+($F$2*$E$2)</f>
-        <v>175812</v>
+        <v>178809</v>
       </c>
       <c r="Q14">
         <f t="shared" ref="Q14:Q15" si="2">1000/(T14-M14)</f>
-        <v>76.92307692307692</v>
+        <v>54.731541787532151</v>
       </c>
       <c r="R14">
-        <f t="shared" ref="R14:R15" si="3">U14*Q14</f>
-        <v>76.92307692307692</v>
+        <f>U14*Q14</f>
+        <v>54.731541787532151</v>
       </c>
       <c r="S14">
-        <f t="shared" ref="S14:S15" si="4">Q14*10^6/P14</f>
-        <v>437.53029897320386</v>
+        <f t="shared" ref="S14:S15" si="3">Q14*10^6/P14</f>
+        <v>306.08941265558303</v>
       </c>
       <c r="T14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U14">
         <v>1</v>
@@ -1061,28 +1107,358 @@
       <c r="C15" t="s">
         <v>49</v>
       </c>
+      <c r="D15">
+        <v>255</v>
+      </c>
+      <c r="E15">
+        <v>2481.29638671875</v>
+      </c>
+      <c r="F15">
+        <v>49.812614440917898</v>
+      </c>
+      <c r="G15">
+        <v>0.29470688797607902</v>
+      </c>
+      <c r="H15">
+        <v>14.1840186355345</v>
+      </c>
+      <c r="I15">
+        <v>54135</v>
+      </c>
+      <c r="J15">
+        <v>28425</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>110</v>
+      </c>
+      <c r="M15">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="N15">
+        <v>3009</v>
+      </c>
+      <c r="O15">
+        <v>182668</v>
+      </c>
       <c r="P15">
         <f t="shared" si="1"/>
-        <v>175812</v>
+        <v>178821</v>
       </c>
       <c r="Q15">
         <f t="shared" si="2"/>
-        <v>76.92307692307692</v>
+        <v>50.893175225202299</v>
       </c>
       <c r="R15">
+        <f t="shared" ref="R14:R15" si="4">U15*Q15</f>
+        <v>50.893175225202299</v>
+      </c>
+      <c r="S15">
         <f t="shared" si="3"/>
-        <v>76.92307692307692</v>
-      </c>
-      <c r="S15">
-        <f t="shared" si="4"/>
-        <v>437.53029897320386</v>
+        <v>284.60401868461923</v>
       </c>
       <c r="T15">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U15">
         <v>1</v>
       </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C19" s="10"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.45">
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
